--- a/docs/计算-蓄电池-深圳.xlsx
+++ b/docs/计算-蓄电池-深圳.xlsx
@@ -432,14 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.036</v>
+        <v>2.04</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P_PV=E_AC/(H_tilt·η_path)=6.99/(4.46×0.77)</t>
+          <t>P_PV=E_AC/(H_tilt·η_path)=6.99/(4.46×0.77)=2.036≈2.04</t>
         </is>
       </c>
     </row>
@@ -822,57 +822,57 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>modA_vol</t>
+          <t>I_ctrl_out_max</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>51.2</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>方案A 模块标称电压（Benhoo BNP-5120BM）</t>
+          <t>MPPT 控制器最大输出（充电）电流</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>benhoobattery.com（查询日期 2026-09-01）</t>
+          <t>W6 控制器选型后回填（暂按典型 100A）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>modA_ah</t>
+          <t>modA_vol</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>100</v>
+        <v>51.2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ah</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>方案A 模块标称容量</t>
+          <t>方案A 模块标称电压（Benhoo BNP-5120BM）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>benhoobattery.com（查询日期 2026-09-01）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>modA_idis</t>
+          <t>modA_ah</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -880,12 +880,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Ah</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>方案A 模块最大连续放电电流</t>
+          <t>方案A 模块标称容量</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -897,11 +897,11 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>modA_ichg</t>
+          <t>modA_idis</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>方案A 模块最大充电电流</t>
+          <t>方案A 模块最大连续放电电流</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -922,95 +922,95 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>modA_price</t>
+          <t>modA_ichg</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>方案A 单模块参考价（区间中值）</t>
+          <t>方案A 模块最大充电电流</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Alibaba 同类 51.2V 100Ah 机架式电池 B2B 报价 ¥3,500~5,000</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>modB_vol</t>
+          <t>modA_price</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>51.2</v>
+        <v>4000</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>元</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>方案B 模块标称电压</t>
+          <t>方案A 单模块参考价（区间中值）</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>madeinchina.com（查询日期 2026-09-01）</t>
+          <t>Alibaba 同类 51.2V 100Ah 机架式电池 B2B 报价 ¥3,500~5,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>modB_ah</t>
+          <t>modB_vol</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>200</v>
+        <v>51.2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Ah</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>方案B 模块标称容量</t>
+          <t>方案B 模块标称电压</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>madeinchina.com（查询日期 2026-09-01）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>modB_idis</t>
+          <t>modB_ah</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Ah</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>方案B 模块最大连续放电电流（0.5C 典型，待规格书确认）</t>
+          <t>方案B 模块标称容量</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>modB_ichg</t>
+          <t>modB_idis</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>方案B 模块最大充电电流（0.5C 典型，待规格书确认）</t>
+          <t>方案B 模块最大连续放电电流（0.5C 典型，待规格书确认）</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1047,23 +1047,48 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>modB_ichg</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>方案B 模块最大充电电流（0.5C 典型，待规格书确认）</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>modB_price</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>6400</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>方案B 单模块参考价（$900 出厂价折算）</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>madeinchina.com 报价 $900 ≈ ¥6,400</t>
         </is>
@@ -1084,8 +1109,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1098,12 +1123,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>公式</t>
+          <t>公式（文字说明）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>结果</t>
+          <t>结果（公式）</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1123,9 +1148,10 @@
           <t>最低标称能量 E_bat,min</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <f>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*K_T)</f>
-        <v/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>E_AC*N_A*K_R/(DOD*eta_dis*eta_inv*K_T)</t>
+        </is>
       </c>
       <c r="C2" s="3">
         <f>参数!B2*参数!B3*参数!B4/(参数!B5*参数!B6*参数!B7*参数!B8)</f>
@@ -1148,9 +1174,10 @@
           <t>最低容量 C_bat,min</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <f>1000*E_bat,min/V_nom</f>
-        <v/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1000*E_bat,min/V_nom</t>
+        </is>
       </c>
       <c r="C3" s="3">
         <f>1000*B2/参数!B9</f>
@@ -1173,12 +1200,13 @@
           <t>方案A 单模块能量 E_modA</t>
         </is>
       </c>
-      <c r="B4" s="2">
-        <f>V_modA*Ah_modA/1000</f>
-        <v/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>V_modA*Ah_modA/1000</t>
+        </is>
       </c>
       <c r="C4" s="3">
-        <f>参数!B16*参数!B17/1000</f>
+        <f>参数!B17*参数!B18/1000</f>
         <v/>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1198,9 +1226,10 @@
           <t>方案A 并联数量(能量) NP,E</t>
         </is>
       </c>
-      <c r="B5" s="2">
-        <f>CEILING(E_bat,min/E_modA,1)</f>
-        <v/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CEILING(E_bat,min/E_modA,1)</t>
+        </is>
       </c>
       <c r="C5" s="3">
         <f>CEILING(B2/B4,1)</f>
@@ -1223,9 +1252,10 @@
           <t>方案A 实际标称能量</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>NP,E*E_modA</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NP,E*E_modA</t>
+        </is>
       </c>
       <c r="C6" s="3">
         <f>B5*B4</f>
@@ -1244,9 +1274,10 @@
           <t>方案A 连续放电电流 I_dis</t>
         </is>
       </c>
-      <c r="B7" s="2">
-        <f>P_inv_r*1000/(V_bat_min*eta_inv)</f>
-        <v/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>P_inv_r*1000/(V_bat_min*eta_inv)</t>
+        </is>
       </c>
       <c r="C7" s="3">
         <f>参数!B12*1000/(参数!B10*参数!B7)</f>
@@ -1269,9 +1300,10 @@
           <t>方案A 短时放电电流</t>
         </is>
       </c>
-      <c r="B8" s="2">
-        <f>P_sur*1000/(V_bat_min*eta_inv)</f>
-        <v/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>P_sur*1000/(V_bat_min*eta_inv)</t>
+        </is>
       </c>
       <c r="C8" s="3">
         <f>参数!B13*1000/(参数!B10*参数!B7)</f>
@@ -1294,12 +1326,13 @@
           <t>方案A 最大充电电流 I_chg</t>
         </is>
       </c>
-      <c r="B9" s="2">
-        <f>MIN(P_PV*1000*eta_MPPT/V_bat_chg, NP,E*modA_ichg)</f>
-        <v/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>MIN(P_PV*1000*eta_MPPT/V_bat_chg, I_ctrl_out_max)</t>
+        </is>
       </c>
       <c r="C9" s="3">
-        <f>MIN(参数!B14*1000*参数!B15/参数!B11, B5*参数!B19)</f>
+        <f>MIN(参数!B14*1000*参数!B15/参数!B11, 参数!B16)</f>
         <v/>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1309,7 +1342,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>指导书 §5.4</t>
+          <t>指导书 §5.4；第二项=控制器输出限流（W6 回填）</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1352,13 @@
           <t>方案A 并联数量(放电)</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>CEILING(I_dis/modA_idis,1)</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CEILING(I_dis/modA_idis,1)</t>
+        </is>
       </c>
       <c r="C10" s="3">
-        <f>CEILING(B7/参数!B18,1)</f>
+        <f>CEILING(B7/参数!B19,1)</f>
         <v/>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1340,12 +1374,13 @@
           <t>方案A 并联数量(充电)</t>
         </is>
       </c>
-      <c r="B11" s="2">
-        <f>CEILING(I_chg/modA_ichg,1)</f>
-        <v/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CEILING(I_chg/modA_ichg,1)</t>
+        </is>
       </c>
       <c r="C11" s="3">
-        <f>CEILING(B9/参数!B19,1)</f>
+        <f>CEILING(B9/参数!B20,1)</f>
         <v/>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1361,9 +1396,10 @@
           <t>方案A 最终并联数量 NP</t>
         </is>
       </c>
-      <c r="B12" s="2">
-        <f>MAX(NP,E,NP,dis,NP,chg)</f>
-        <v/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>MAX(NP,E,NP,dis,NP,chg)</t>
+        </is>
       </c>
       <c r="C12" s="3">
         <f>MAX(B5,B10,B11)</f>
@@ -1386,9 +1422,10 @@
           <t>方案A 配置</t>
         </is>
       </c>
-      <c r="B13" s="2">
-        <f>"51.2V 100Ah×"&amp;NP</f>
-        <v/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>"51.2V 100Ah×"&amp;NP</t>
+        </is>
       </c>
       <c r="C13" s="3">
         <f>"51.2V 100Ah×"&amp;B12</f>
@@ -1407,12 +1444,13 @@
           <t>方案A 成本(模块)</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>NP*modA_price</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NP*modA_price</t>
+        </is>
       </c>
       <c r="C14" s="3">
-        <f>B12*参数!B20</f>
+        <f>B12*参数!B21</f>
         <v/>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1432,9 +1470,10 @@
           <t>3d 标称能量</t>
         </is>
       </c>
-      <c r="B15" s="2">
-        <f>E_AC*3*K_R/(DOD*eta_dis*eta_inv*K_T)</f>
-        <v/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>E_AC*3*K_R/(DOD*eta_dis*eta_inv*K_T)</t>
+        </is>
       </c>
       <c r="C15" s="3">
         <f>参数!B2*3*参数!B4/(参数!B5*参数!B6*参数!B7*参数!B8)</f>
@@ -1457,9 +1496,10 @@
           <t>3d/2d 比值</t>
         </is>
       </c>
-      <c r="B16" s="2">
-        <f>B15/B2</f>
-        <v/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>E_3d/E_bat,min</t>
+        </is>
       </c>
       <c r="C16" s="3">
         <f>B15/B2</f>
@@ -1482,12 +1522,13 @@
           <t>方案B 单模块能量 E_modB</t>
         </is>
       </c>
-      <c r="B17" s="2">
-        <f>V_modB*Ah_modB/1000</f>
-        <v/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>V_modB*Ah_modB/1000</t>
+        </is>
       </c>
       <c r="C17" s="3">
-        <f>参数!B21*参数!B22/1000</f>
+        <f>参数!B22*参数!B23/1000</f>
         <v/>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1503,9 +1544,10 @@
           <t>方案B 并联数量(能量)</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>CEILING(E_bat,min/E_modB,1)</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CEILING(E_bat,min/E_modB,1)</t>
+        </is>
       </c>
       <c r="C18" s="3">
         <f>CEILING(B2/B17,1)</f>
@@ -1524,9 +1566,10 @@
           <t>方案B 实际标称能量</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <f>NP,E_B*E_modB</f>
-        <v/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NP,E_B*E_modB</t>
+        </is>
       </c>
       <c r="C19" s="3">
         <f>B18*B17</f>
@@ -1545,9 +1588,10 @@
           <t>方案B 配置</t>
         </is>
       </c>
-      <c r="B20" s="2">
-        <f>"51.2V 200Ah×"&amp;NP,E_B</f>
-        <v/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>"51.2V 200Ah×"&amp;NP,E_B</t>
+        </is>
       </c>
       <c r="C20" s="3">
         <f>"51.2V 200Ah×"&amp;B18</f>
@@ -1566,12 +1610,13 @@
           <t>方案B 成本(模块)</t>
         </is>
       </c>
-      <c r="B21" s="2">
-        <f>NP,E_B*modB_price</f>
-        <v/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NP,E_B*modB_price</t>
+        </is>
       </c>
       <c r="C21" s="3">
-        <f>B18*参数!B25</f>
+        <f>B18*参数!B26</f>
         <v/>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1596,8 +1641,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1629,10 +1674,9 @@
           <t>最低标称能量</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
+      <c r="B2" s="2">
+        <f>容量计算!C2</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -1653,7 +1697,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>方案A 待定（调研回填）</t>
+          <t>Benhoo BNP-5120BM（51.2V 100Ah，5.12kWh）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1693,19 +1737,18 @@
           <t>并联数量</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
+      <c r="B5" s="2">
+        <f>容量计算!C12</f>
+        <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>≤厂家最大并联</t>
+          <t>≤75 台（厂家标注）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1715,18 +1758,16 @@
           <t>实际标称能量</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>≤1.25×B2</t>
-        </is>
+      <c r="B6" s="2">
+        <f>容量计算!C6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
+        <f>1.25*容量计算!C2</f>
+        <v/>
       </c>
       <c r="D6" s="2">
-        <f>IF(B6&lt;=1.25*B2,"OK","超标")</f>
+        <f>IF(B6&lt;=C6,"OK","超标")</f>
         <v/>
       </c>
     </row>
@@ -1736,17 +1777,16 @@
           <t>连续放电电流</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
+      <c r="B7" s="2">
+        <f>容量计算!C7</f>
+        <v/>
       </c>
       <c r="C7" s="2">
-        <f>B12*参数!B18</f>
+        <f>容量计算!C12*参数!B19</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>IF(B7&lt;=B12*参数!B18,"OK","不足")</f>
+        <f>IF(B7&lt;=C7,"OK","不足")</f>
         <v/>
       </c>
     </row>
@@ -1756,20 +1796,17 @@
           <t>短时放电电流</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>（厂家峰值限值）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
+      <c r="B8" s="2">
+        <f>容量计算!C8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>容量计算!C12*参数!B19</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>IF(B8&lt;=C8,"OK","不足")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1778,17 +1815,16 @@
           <t>最大充电电流</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
+      <c r="B9" s="2">
+        <f>容量计算!C9</f>
+        <v/>
       </c>
       <c r="C9" s="2">
-        <f>B12*参数!B19</f>
+        <f>容量计算!C12*参数!B20</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>IF(B9&lt;=B12*参数!B19,"OK","不足")</f>
+        <f>IF(B9&lt;=C9,"OK","不足")</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +1836,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>内部BMS×N，并联须厂家允许</t>
+          <t>智能BMS（RS485/CAN），并联 4 台</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1810,7 +1846,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1820,10 +1856,9 @@
           <t>2d/3d 对比</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
+      <c r="B11" s="2">
+        <f>容量计算!C15</f>
+        <v/>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1831,7 +1866,7 @@
         </is>
       </c>
       <c r="D11" s="2">
-        <f>IF(ABS(B16-1.5)&lt;0.01,"OK","复核")</f>
+        <f>IF(ABS(B11/容量计算!C2-1.5)&lt;0.01,"OK","复核")</f>
         <v/>
       </c>
     </row>

--- a/docs/计算-蓄电池-深圳.xlsx
+++ b/docs/计算-蓄电池-深圳.xlsx
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>任务书示例 0.92 / W3 效率表</t>
+          <t>Growatt SPF 5000 ES 官方峰值效率 93%（W6 回填）；原任务书示例 0.92 为保守口径</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>逆变器规格书（W6 回填）；与模块放电下限 44.8V 一致</t>
+          <t>逆变器低压切断须设置 &gt;=44.8V（W6 确认）；与模块放电下限 44.8V 一致</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>逆变器额定功率（暂定 5kW，W6 选型后回填）</t>
+          <t>逆变器额定功率（SPF 5000 ES）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P_max=3.0kW×1.67 裕量；拟选 Growatt SPF 5000 ES 或同级</t>
+          <t>Growatt SPF 5000 ES 额定 5kW（W6 官方确认）；P_max=3.0kW x 1.67 裕量</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -785,12 +785,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>光伏阵列容量预估（W5 回填）</t>
+          <t>光伏阵列装机容量（W5 定案）</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P_PV=E_AC/(H_tilt·η_path)=6.99/(4.46×0.77)=2.036≈2.04</t>
+          <t>W5 定案 P_PV=2.40 kWp（4串x1并 600W）；I_chg 复核 42.4A</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>W6 控制器选型后回填（暂按典型 100A）</t>
+          <t>SPF 5000 ES 最大太阳能充电电流 100A（W6 官方确认）</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <f>1000*B2/参数!B9</f>
+        <f>1000*C2/参数!B9</f>
         <v/>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>CEILING(B2/B4,1)</f>
+        <f>CEILING(C2/C4,1)</f>
         <v/>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>B5*B4</f>
+        <f>C5*C4</f>
         <v/>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C10" s="3">
-        <f>CEILING(B7/参数!B19,1)</f>
+        <f>CEILING(C7/参数!B19,1)</f>
         <v/>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <f>CEILING(B9/参数!B20,1)</f>
+        <f>CEILING(C9/参数!B20,1)</f>
         <v/>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C12" s="3">
-        <f>MAX(B5,B10,B11)</f>
+        <f>MAX(C5,C10,C11)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>"51.2V 100Ah×"&amp;B12</f>
+        <f>"51.2V 100Ah×"&amp;C12</f>
         <v/>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="C14" s="3">
-        <f>B12*参数!B21</f>
+        <f>C12*参数!B21</f>
         <v/>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="C16" s="3">
-        <f>B15/B2</f>
+        <f>C15/C2</f>
         <v/>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C18" s="3">
-        <f>CEILING(B2/B17,1)</f>
+        <f>CEILING(C2/C17,1)</f>
         <v/>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C19" s="3">
-        <f>B18*B17</f>
+        <f>C18*C17</f>
         <v/>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C20" s="3">
-        <f>"51.2V 200Ah×"&amp;B18</f>
+        <f>"51.2V 200Ah×"&amp;C18</f>
         <v/>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C21" s="3">
-        <f>B18*参数!B26</f>
+        <f>C18*参数!B26</f>
         <v/>
       </c>
       <c r="D21" s="2" t="inlineStr">
